--- a/codes/data/2025/Apr_11/lifetime_values.xlsx
+++ b/codes/data/2025/Apr_11/lifetime_values.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\Atanu_experiments\T1_measurements\codes\data\2025\Apr_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60200E85-1AF9-40AD-9595-9C322C3E8E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E6DA57-1772-4D51-B317-E47D9291963E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6BAC496-8775-4DEB-810F-11145EE53287}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D6BAC496-8775-4DEB-810F-11145EE53287}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>power</t>
   </si>
@@ -83,6 +84,9 @@
   </si>
   <si>
     <t xml:space="preserve">Intially we have taken bare nanodiamond sample mixed with water for T1 relaxation ex[periment. The result we found around average of 60. Then we applied 10 micro liter of Gd solution  to it and taken again the measurement shows little more average than bare one i.e. 70.  Then we have added concentrated Gd solution to the same cluster and we found T1 measurement decreases  average of 47. But after some time (like 10 min) it increases dramatically. </t>
+  </si>
+  <si>
+    <t>initialization times</t>
   </si>
 </sst>
 </file>
@@ -830,6 +834,47 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823C3D4D-FD08-491D-ADA7-DDBBD0BD65A0}">
+  <dimension ref="D3:K5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>50</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4170B57-3D3E-485A-9A62-A4503C378F25}">
   <dimension ref="D3:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
